--- a/doc/justificacion.xlsx
+++ b/doc/justificacion.xlsx
@@ -5742,7 +5742,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-PE"/>
           </a:p>
@@ -5833,7 +5833,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-PE"/>
           </a:p>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="C4" s="140" t="inlineStr">
         <is>
-          <t>Nueva SpotLoad ×1 — PA217</t>
+          <t>San Fernando S.A (RUC 20100154308)</t>
         </is>
       </c>
       <c r="D4" s="140" t="n"/>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="C5" s="140" t="inlineStr">
         <is>
-          <t>Electro Dunas</t>
+          <t>Sector Santa Fe de Lanchas,  Unidad Catastral 72869, distrito de Paracas, provincia de Pisco y departamento de Ica</t>
         </is>
       </c>
       <c r="D5" s="140" t="n"/>
@@ -15433,14 +15433,14 @@
       </c>
       <c r="C6" s="140" t="inlineStr">
         <is>
-          <t>Factibilidad y Punto de Diseño</t>
+          <t>Solicitud de factibilidad y punto de diseño en media tensión</t>
         </is>
       </c>
       <c r="D6" s="140" t="n"/>
       <c r="E6" s="140" t="n"/>
       <c r="H6" s="350" t="inlineStr">
         <is>
-          <t>1500KW</t>
+          <t>1420KW</t>
         </is>
       </c>
       <c r="I6" s="350" t="n"/>
@@ -15452,7 +15452,7 @@
         </is>
       </c>
       <c r="C7" s="494" t="n">
-        <v>1500</v>
+        <v>1420</v>
       </c>
       <c r="G7" s="141" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         </is>
       </c>
       <c r="H7" s="373" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="8">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="H8" s="137" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>SET Paracas</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="H9" s="137" t="inlineStr">
         <is>
-          <t xml:space="preserve">50/30/30  MVA - ONAN </t>
+          <t>Transformador SET Paracas · 22.9 kV (inventario CYMDIST)</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="C10" s="137" t="inlineStr">
         <is>
-          <t>RECYM-PA217</t>
+          <t>CARTA G T-SU-966-2026/PO</t>
         </is>
       </c>
       <c r="D10" s="140" t="n"/>
@@ -15699,15 +15699,15 @@
       <c r="C32" s="610" t="n"/>
       <c r="D32" s="611" t="n"/>
       <c r="E32" s="392">
-        <f>+'Resultados de escenarios'!C5</f>
+        <f>'Resultados de escenarios'!O14</f>
         <v/>
       </c>
       <c r="F32" s="392">
-        <f>+'Resultados de escenarios'!I5</f>
+        <f>'Resultados de escenarios'!P14</f>
         <v/>
       </c>
       <c r="G32" s="392">
-        <f>+'Resultados de escenarios'!G5</f>
+        <f>'Resultados de escenarios'!Q14</f>
         <v/>
       </c>
       <c r="H32" s="393">
@@ -15846,7 +15846,7 @@
     <row r="101">
       <c r="B101" s="143" t="inlineStr">
         <is>
-          <t>2.1 RED PROYECTADA DE ELECTRODUNAS LL202</t>
+          <t>2.1 RED PROYECTADA DE ELECTRODUNAS PA217</t>
         </is>
       </c>
       <c r="C101" s="143" t="n"/>
@@ -16128,7 +16128,7 @@
     <row r="181">
       <c r="B181" s="137" t="inlineStr">
         <is>
-          <t>PERDIDAS OBTENIDAS DE ESTUDIOS REALIZADOS AL ALIMENTADOR SL201 (Incorporando cargas solicitadas)</t>
+          <t>PERDIDAS OBTENIDAS DE ESTUDIOS REALIZADOS AL ALIMENTADOR PA217 (Incorporando cargas solicitadas)</t>
         </is>
       </c>
     </row>
@@ -16188,7 +16188,7 @@
     <row customHeight="1" ht="28.5" r="185">
       <c r="B185" s="480" t="inlineStr">
         <is>
-          <t>ESTADO ACTUAL LL202</t>
+          <t>ESTADO ACTUAL PA217</t>
         </is>
       </c>
       <c r="C185" s="385">
@@ -16215,7 +16215,7 @@
     <row customHeight="1" ht="28.5" r="186">
       <c r="B186" s="480" t="inlineStr">
         <is>
-          <t>ESTADO PRYECTADO LL202</t>
+          <t>ESTADO PROYECTADO PA217</t>
         </is>
       </c>
       <c r="C186" s="385">
@@ -19514,16 +19514,16 @@
         <v>13.2</v>
       </c>
       <c r="F5" s="381" t="n">
-        <v>178.8</v>
+        <v>169.8</v>
       </c>
       <c r="G5" s="381" t="n">
-        <v>7093.52</v>
+        <v>6736.6</v>
       </c>
       <c r="H5" s="381" t="n">
-        <v>6389</v>
+        <v>6498</v>
       </c>
       <c r="I5" s="381" t="n">
-        <v>3082</v>
+        <v>1777</v>
       </c>
     </row>
     <row customFormat="1" r="6" s="153">
@@ -19655,52 +19655,40 @@
           <t>Pérdidas en las líneas</t>
         </is>
       </c>
-      <c r="C12" s="346" t="n">
+      <c r="C12" s="346" t="n"/>
+      <c r="D12" s="164" t="n"/>
+      <c r="E12" s="164" t="n"/>
+      <c r="H12" s="156" t="inlineStr">
+        <is>
+          <t>Sobrecarga</t>
+        </is>
+      </c>
+      <c r="I12" s="343" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J12" s="387" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="164" t="n">
-        <v>63.83</v>
-      </c>
-      <c r="E12" s="164" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="H12" s="156" t="inlineStr">
-        <is>
-          <t>Sobrecarga</t>
-        </is>
-      </c>
-      <c r="I12" s="343" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J12" s="387" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="164" t="inlineStr">
-        <is>
-          <t>SEC_2010_329525_SE70004</t>
-        </is>
-      </c>
-      <c r="L12" s="165" t="n">
-        <v>1.7376</v>
-      </c>
+      <c r="K12" s="164" t="n"/>
+      <c r="L12" s="165" t="n"/>
       <c r="N12" s="170" t="inlineStr">
         <is>
           <t>Fuentes (Potencia de equilibrio)</t>
         </is>
       </c>
       <c r="O12" s="346" t="n">
-        <v>6389</v>
+        <v>6498</v>
       </c>
       <c r="P12" s="164" t="n">
-        <v>3082</v>
+        <v>1777</v>
       </c>
       <c r="Q12" s="164" t="n">
-        <v>7093.52</v>
+        <v>6736.6</v>
       </c>
       <c r="R12" s="164" t="n">
-        <v>90.06999999999999</v>
+        <v>96.45999999999999</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="13" s="153" thickBot="1">
@@ -19725,16 +19713,10 @@
         </is>
       </c>
       <c r="J13" s="388" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="166" t="inlineStr">
-        <is>
-          <t>SEC_2010_329525_SE70004</t>
-        </is>
-      </c>
-      <c r="L13" s="167" t="n">
-        <v>1.7376</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="166" t="n"/>
+      <c r="L13" s="167" t="n"/>
       <c r="N13" s="171" t="inlineStr">
         <is>
           <t>Generadores</t>
@@ -19775,32 +19757,26 @@
         </is>
       </c>
       <c r="J14" s="389" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="168" t="inlineStr">
-        <is>
-          <t>SEC_2010_329525_SE70004</t>
-        </is>
-      </c>
-      <c r="L14" s="169" t="n">
-        <v>1.7376</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K14" s="168" t="n"/>
+      <c r="L14" s="169" t="n"/>
       <c r="N14" s="172" t="inlineStr">
         <is>
           <t>Producción total</t>
         </is>
       </c>
       <c r="O14" s="342" t="n">
-        <v>6389</v>
+        <v>6498</v>
       </c>
       <c r="P14" s="173" t="n">
-        <v>3082</v>
+        <v>1777</v>
       </c>
       <c r="Q14" s="173" t="n">
-        <v>7093.52</v>
+        <v>6736.6</v>
       </c>
       <c r="R14" s="173" t="n">
-        <v>90.06999999999999</v>
+        <v>96.45999999999999</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="15" s="153" thickBot="1">
@@ -19831,11 +19807,7 @@
       <c r="J15" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="166" t="inlineStr">
-        <is>
-          <t>NODE_2010_329638_SE70063_VIRTUAL</t>
-        </is>
-      </c>
+      <c r="K15" s="166" t="n"/>
       <c r="L15" s="167" t="n">
         <v>0.9984</v>
       </c>
@@ -19845,16 +19817,16 @@
         </is>
       </c>
       <c r="O15" s="347" t="n">
-        <v>6389</v>
+        <v>6498</v>
       </c>
       <c r="P15" s="166" t="n">
-        <v>3082</v>
+        <v>1777</v>
       </c>
       <c r="Q15" s="166" t="n">
-        <v>7093.52</v>
+        <v>6736.6</v>
       </c>
       <c r="R15" s="166" t="n">
-        <v>90.06999999999999</v>
+        <v>96.45999999999999</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="16" s="153" thickBot="1">
@@ -19863,15 +19835,9 @@
           <t>Pérdidas totales</t>
         </is>
       </c>
-      <c r="C16" s="342" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="173" t="n">
-        <v>63.83</v>
-      </c>
-      <c r="E16" s="173" t="n">
-        <v>6.38</v>
-      </c>
+      <c r="C16" s="342" t="n"/>
+      <c r="D16" s="173" t="n"/>
+      <c r="E16" s="173" t="n"/>
       <c r="H16" s="157" t="n"/>
       <c r="I16" s="344" t="inlineStr">
         <is>
@@ -19881,11 +19847,7 @@
       <c r="J16" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="166" t="inlineStr">
-        <is>
-          <t>NODE_2010_329580_SE70029_VIRTUAL</t>
-        </is>
-      </c>
+      <c r="K16" s="166" t="n"/>
       <c r="L16" s="167" t="n">
         <v>0.9984</v>
       </c>
@@ -19895,16 +19857,16 @@
         </is>
       </c>
       <c r="O16" s="347" t="n">
-        <v>6389</v>
+        <v>6498</v>
       </c>
       <c r="P16" s="166" t="n">
-        <v>3082</v>
+        <v>1777</v>
       </c>
       <c r="Q16" s="166" t="n">
-        <v>7093.52</v>
+        <v>6736.6</v>
       </c>
       <c r="R16" s="166" t="n">
-        <v>90.06999999999999</v>
+        <v>96.45999999999999</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="17" s="153" thickBot="1">
@@ -19917,11 +19879,7 @@
       <c r="J17" s="389" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="168" t="inlineStr">
-        <is>
-          <t>NODE_2010_329638_SE70063_VIRTUAL</t>
-        </is>
-      </c>
+      <c r="K17" s="168" t="n"/>
       <c r="L17" s="169" t="n">
         <v>0.9984</v>
       </c>
@@ -19963,14 +19921,8 @@
       <c r="J18" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="166" t="inlineStr">
-        <is>
-          <t>NET_2030_147_LL202</t>
-        </is>
-      </c>
-      <c r="L18" s="167" t="n">
-        <v>1.0483</v>
-      </c>
+      <c r="K18" s="166" t="n"/>
+      <c r="L18" s="167" t="n"/>
       <c r="N18" s="171" t="inlineStr">
         <is>
           <t>Reactancias shunt(reguladas)</t>
@@ -20005,14 +19957,8 @@
       <c r="J19" s="387" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="164" t="inlineStr">
-        <is>
-          <t>NET_2030_147_LL202</t>
-        </is>
-      </c>
-      <c r="L19" s="165" t="n">
-        <v>1.0483</v>
-      </c>
+      <c r="K19" s="164" t="n"/>
+      <c r="L19" s="165" t="n"/>
       <c r="N19" s="171" t="inlineStr">
         <is>
           <t>Motores</t>
@@ -20047,14 +19993,8 @@
       <c r="J20" s="389" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="168" t="inlineStr">
-        <is>
-          <t>NET_2030_147_LL202</t>
-        </is>
-      </c>
-      <c r="L20" s="169" t="n">
-        <v>1.0483</v>
-      </c>
+      <c r="K20" s="168" t="n"/>
+      <c r="L20" s="169" t="n"/>
       <c r="M20" s="177" t="n"/>
       <c r="N20" s="172" t="inlineStr">
         <is>
@@ -20062,16 +20002,16 @@
         </is>
       </c>
       <c r="O20" s="342" t="n">
-        <v>6389</v>
+        <v>6498</v>
       </c>
       <c r="P20" s="173" t="n">
-        <v>3082</v>
+        <v>1777</v>
       </c>
       <c r="Q20" s="173" t="n">
-        <v>7093.52</v>
+        <v>6736.6</v>
       </c>
       <c r="R20" s="173" t="n">
-        <v>90.06999999999999</v>
+        <v>96.45999999999999</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="21" s="153" thickBot="1">
@@ -20085,18 +20025,10 @@
           <t>Capacitancia del cable</t>
         </is>
       </c>
-      <c r="O21" s="346" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="164" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="Q21" s="164" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="R21" s="164" t="n">
-        <v>0</v>
-      </c>
+      <c r="O21" s="346" t="n"/>
+      <c r="P21" s="164" t="n"/>
+      <c r="Q21" s="164" t="n"/>
+      <c r="R21" s="164" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="22" s="153" thickBot="1">
       <c r="I22" s="174" t="n"/>
@@ -20109,18 +20041,10 @@
           <t>Capacitancia de la línea</t>
         </is>
       </c>
-      <c r="O22" s="347" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="166" t="n">
-        <v>-7.64</v>
-      </c>
-      <c r="Q22" s="166" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="R22" s="166" t="n">
-        <v>0</v>
-      </c>
+      <c r="O22" s="347" t="n"/>
+      <c r="P22" s="166" t="n"/>
+      <c r="Q22" s="166" t="n"/>
+      <c r="R22" s="166" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="23" s="153" thickBot="1">
       <c r="I23" s="174" t="n"/>
@@ -20133,18 +20057,10 @@
           <t>Capacitancia shunt total</t>
         </is>
       </c>
-      <c r="O23" s="342" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="173" t="n">
-        <v>-15.88</v>
-      </c>
-      <c r="Q23" s="173" t="n">
-        <v>15.88</v>
-      </c>
-      <c r="R23" s="173" t="n">
-        <v>0</v>
-      </c>
+      <c r="O23" s="342" t="n"/>
+      <c r="P23" s="173" t="n"/>
+      <c r="Q23" s="173" t="n"/>
+      <c r="R23" s="173" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="24" s="153" thickBot="1">
       <c r="A24" s="179" t="n"/>
@@ -20158,18 +20074,10 @@
           <t>Pérdidas en las líneas</t>
         </is>
       </c>
-      <c r="O24" s="347" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="166" t="n">
-        <v>0</v>
-      </c>
+      <c r="O24" s="347" t="n"/>
+      <c r="P24" s="166" t="n"/>
+      <c r="Q24" s="166" t="n"/>
+      <c r="R24" s="166" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="25" s="153" thickBot="1">
       <c r="A25" s="179" t="n"/>
@@ -20183,18 +20091,10 @@
           <t>Pérdidas en los cables</t>
         </is>
       </c>
-      <c r="O25" s="347" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P25" s="166" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="Q25" s="166" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R25" s="166" t="n">
-        <v>77.38</v>
-      </c>
+      <c r="O25" s="347" t="n"/>
+      <c r="P25" s="166" t="n"/>
+      <c r="Q25" s="166" t="n"/>
+      <c r="R25" s="166" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="26" s="153" thickBot="1">
       <c r="A26" s="179" t="n"/>
@@ -20208,18 +20108,10 @@
           <t>Pérdidas de carga del transformador</t>
         </is>
       </c>
-      <c r="O26" s="347" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="166" t="n">
-        <v>0</v>
-      </c>
+      <c r="O26" s="347" t="n"/>
+      <c r="P26" s="166" t="n"/>
+      <c r="Q26" s="166" t="n"/>
+      <c r="R26" s="166" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="27" s="153" thickBot="1">
       <c r="A27" s="179" t="n"/>
@@ -20233,18 +20125,10 @@
           <t>Pérdidas en vacío del transformador</t>
         </is>
       </c>
-      <c r="O27" s="347" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="166" t="n">
-        <v>0</v>
-      </c>
+      <c r="O27" s="347" t="n"/>
+      <c r="P27" s="166" t="n"/>
+      <c r="Q27" s="166" t="n"/>
+      <c r="R27" s="166" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="28" s="153" thickBot="1">
       <c r="A28" s="179" t="n"/>
@@ -20258,18 +20142,10 @@
           <t>Pérdidas totales</t>
         </is>
       </c>
-      <c r="O28" s="342" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="173" t="n">
-        <v>0</v>
-      </c>
+      <c r="O28" s="342" t="n"/>
+      <c r="P28" s="173" t="n"/>
+      <c r="Q28" s="173" t="n"/>
+      <c r="R28" s="173" t="n"/>
     </row>
     <row customFormat="1" r="29" s="153">
       <c r="A29" s="179" t="n"/>
@@ -20345,7 +20221,7 @@
       <c r="A34" s="179" t="n"/>
       <c r="B34" s="504" t="inlineStr">
         <is>
-          <t>ESCENARIO PROYECTADO DEL ALIMENTADOR A LL202</t>
+          <t>ESCENARIO PROYECTADO DEL ALIMENTADOR PA217</t>
         </is>
       </c>
       <c r="I34" s="174" t="n"/>
@@ -20466,25 +20342,25 @@
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="39" s="153" thickBot="1">
       <c r="C39" s="380" t="n">
-        <v>0.99</v>
+        <v>0.9984</v>
       </c>
       <c r="D39" s="381" t="n">
-        <v>9.9</v>
+        <v>22.9</v>
       </c>
       <c r="E39" s="381" t="n">
-        <v>5.7</v>
+        <v>13.2</v>
       </c>
       <c r="F39" s="381" t="n">
-        <v>199</v>
+        <v>169.8</v>
       </c>
       <c r="G39" s="381" t="n">
-        <v>3233.12</v>
+        <v>6736.6</v>
       </c>
       <c r="H39" s="381" t="n">
-        <v>3233.12</v>
+        <v>6498</v>
       </c>
       <c r="I39" s="381" t="n">
-        <v>1156.66</v>
+        <v>1777</v>
       </c>
       <c r="J39" s="175" t="n"/>
       <c r="K39" s="175" t="n"/>
@@ -20675,15 +20551,9 @@
           <t>Pérdidas en las líneas</t>
         </is>
       </c>
-      <c r="C46" s="346" t="n">
-        <v>157.61</v>
-      </c>
-      <c r="D46" s="164" t="n">
-        <v>505.5</v>
-      </c>
-      <c r="E46" s="164" t="n">
-        <v>50.55</v>
-      </c>
+      <c r="C46" s="346" t="n"/>
+      <c r="D46" s="164" t="n"/>
+      <c r="E46" s="164" t="n"/>
       <c r="H46" s="156" t="inlineStr">
         <is>
           <t>Sobrecarga</t>
@@ -20695,32 +20565,26 @@
         </is>
       </c>
       <c r="J46" s="387" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" s="164" t="inlineStr">
-        <is>
-          <t>SEC_2010_329525_SE70004</t>
-        </is>
-      </c>
-      <c r="L46" s="165" t="n">
-        <v>1.7367</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K46" s="164" t="n"/>
+      <c r="L46" s="165" t="n"/>
       <c r="N46" s="170" t="inlineStr">
         <is>
           <t>Fuentes (Potencia de equilibrio)</t>
         </is>
       </c>
       <c r="O46" s="346" t="n">
-        <v>3233.12</v>
+        <v>6498</v>
       </c>
       <c r="P46" s="164" t="n">
-        <v>1156.66</v>
+        <v>1777</v>
       </c>
       <c r="Q46" s="164" t="n">
-        <v>3433.79</v>
+        <v>6736.6</v>
       </c>
       <c r="R46" s="164" t="n">
-        <v>94.16</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="S46" s="175" t="n"/>
     </row>
@@ -20747,16 +20611,10 @@
         </is>
       </c>
       <c r="J47" s="388" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="166" t="inlineStr">
-        <is>
-          <t>SEC_2010_329525_SE70004</t>
-        </is>
-      </c>
-      <c r="L47" s="167" t="n">
-        <v>1.7366</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K47" s="166" t="n"/>
+      <c r="L47" s="167" t="n"/>
       <c r="N47" s="171" t="inlineStr">
         <is>
           <t>Generadores</t>
@@ -20799,32 +20657,26 @@
         </is>
       </c>
       <c r="J48" s="389" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" s="168" t="inlineStr">
-        <is>
-          <t>SEC_2010_329525_SE70004</t>
-        </is>
-      </c>
-      <c r="L48" s="169" t="n">
-        <v>1.7368</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K48" s="168" t="n"/>
+      <c r="L48" s="169" t="n"/>
       <c r="N48" s="172" t="inlineStr">
         <is>
           <t>Producción total</t>
         </is>
       </c>
       <c r="O48" s="342" t="n">
-        <v>3233.12</v>
+        <v>6498</v>
       </c>
       <c r="P48" s="173" t="n">
-        <v>1156.66</v>
+        <v>1777</v>
       </c>
       <c r="Q48" s="173" t="n">
-        <v>3433.79</v>
+        <v>6736.6</v>
       </c>
       <c r="R48" s="173" t="n">
-        <v>94.16</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="S48" s="175" t="n"/>
     </row>
@@ -20857,11 +20709,9 @@
       <c r="J49" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="166" t="n">
-        <v>37</v>
-      </c>
+      <c r="K49" s="166" t="n"/>
       <c r="L49" s="167" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="N49" s="171" t="inlineStr">
         <is>
@@ -20869,16 +20719,16 @@
         </is>
       </c>
       <c r="O49" s="347" t="n">
-        <v>3182.04</v>
+        <v>6498</v>
       </c>
       <c r="P49" s="166" t="n">
-        <v>1101.44</v>
+        <v>1777</v>
       </c>
       <c r="Q49" s="166" t="n">
-        <v>3367.28</v>
+        <v>6736.6</v>
       </c>
       <c r="R49" s="166" t="n">
-        <v>94.5</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="S49" s="175" t="n"/>
     </row>
@@ -20889,15 +20739,9 @@
           <t>Pérdidas totales</t>
         </is>
       </c>
-      <c r="C50" s="342" t="n">
-        <v>157.61</v>
-      </c>
-      <c r="D50" s="173" t="n">
-        <v>505.5</v>
-      </c>
-      <c r="E50" s="173" t="n">
-        <v>50.55</v>
-      </c>
+      <c r="C50" s="342" t="n"/>
+      <c r="D50" s="173" t="n"/>
+      <c r="E50" s="173" t="n"/>
       <c r="H50" s="157" t="n"/>
       <c r="I50" s="344" t="inlineStr">
         <is>
@@ -20907,11 +20751,9 @@
       <c r="J50" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K50" s="166" t="n">
-        <v>37</v>
-      </c>
+      <c r="K50" s="166" t="n"/>
       <c r="L50" s="167" t="n">
-        <v>0.9599</v>
+        <v>0.9984</v>
       </c>
       <c r="N50" s="171" t="inlineStr">
         <is>
@@ -20919,16 +20761,16 @@
         </is>
       </c>
       <c r="O50" s="347" t="n">
-        <v>3182</v>
+        <v>6498</v>
       </c>
       <c r="P50" s="166" t="n">
-        <v>1101.38</v>
+        <v>1777</v>
       </c>
       <c r="Q50" s="166" t="n">
-        <v>3367.22</v>
+        <v>6736.6</v>
       </c>
       <c r="R50" s="166" t="n">
-        <v>94.5</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="S50" s="175" t="n"/>
     </row>
@@ -20943,11 +20785,9 @@
       <c r="J51" s="389" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="168" t="n">
-        <v>37</v>
-      </c>
+      <c r="K51" s="168" t="n"/>
       <c r="L51" s="169" t="n">
-        <v>0.9643</v>
+        <v>0.9984</v>
       </c>
       <c r="N51" s="171" t="inlineStr">
         <is>
@@ -20989,14 +20829,8 @@
       <c r="J52" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="166" t="inlineStr">
-        <is>
-          <t>NET_2030_147_LL202</t>
-        </is>
-      </c>
-      <c r="L52" s="167" t="n">
-        <v>1.0483</v>
-      </c>
+      <c r="K52" s="166" t="n"/>
+      <c r="L52" s="167" t="n"/>
       <c r="N52" s="171" t="inlineStr">
         <is>
           <t>Reactancias shunt(reguladas)</t>
@@ -21033,14 +20867,8 @@
       <c r="J53" s="387" t="n">
         <v>0</v>
       </c>
-      <c r="K53" s="164" t="inlineStr">
-        <is>
-          <t>NET_2030_147_LL202</t>
-        </is>
-      </c>
-      <c r="L53" s="165" t="n">
-        <v>1.0483</v>
-      </c>
+      <c r="K53" s="164" t="n"/>
+      <c r="L53" s="165" t="n"/>
       <c r="N53" s="171" t="inlineStr">
         <is>
           <t>Motores</t>
@@ -21077,14 +20905,8 @@
       <c r="J54" s="389" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="168" t="inlineStr">
-        <is>
-          <t>NET_2030_147_LL202</t>
-        </is>
-      </c>
-      <c r="L54" s="169" t="n">
-        <v>1.0483</v>
-      </c>
+      <c r="K54" s="168" t="n"/>
+      <c r="L54" s="169" t="n"/>
       <c r="M54" s="177" t="n"/>
       <c r="N54" s="172" t="inlineStr">
         <is>
@@ -21092,16 +20914,16 @@
         </is>
       </c>
       <c r="O54" s="342" t="n">
-        <v>3182</v>
+        <v>6498</v>
       </c>
       <c r="P54" s="173" t="n">
-        <v>1101.38</v>
+        <v>1777</v>
       </c>
       <c r="Q54" s="173" t="n">
-        <v>3367.22</v>
+        <v>6736.6</v>
       </c>
       <c r="R54" s="173" t="n">
-        <v>94.5</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="S54" s="175" t="n"/>
     </row>
@@ -21117,18 +20939,10 @@
           <t>Capacitancia del cable</t>
         </is>
       </c>
-      <c r="O55" s="346" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="164" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="Q55" s="164" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="R55" s="164" t="n">
-        <v>0</v>
-      </c>
+      <c r="O55" s="346" t="n"/>
+      <c r="P55" s="164" t="n"/>
+      <c r="Q55" s="164" t="n"/>
+      <c r="R55" s="164" t="n"/>
       <c r="S55" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="56" s="153" thickBot="1">
@@ -21143,18 +20957,10 @@
           <t>Capacitancia de la línea</t>
         </is>
       </c>
-      <c r="O56" s="347" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="166" t="n">
-        <v>-7.61</v>
-      </c>
-      <c r="Q56" s="166" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="R56" s="166" t="n">
-        <v>0</v>
-      </c>
+      <c r="O56" s="347" t="n"/>
+      <c r="P56" s="166" t="n"/>
+      <c r="Q56" s="166" t="n"/>
+      <c r="R56" s="166" t="n"/>
       <c r="S56" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="57" s="153" thickBot="1">
@@ -21169,18 +20975,10 @@
           <t>Capacitancia shunt total</t>
         </is>
       </c>
-      <c r="O57" s="342" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="173" t="n">
-        <v>-15.81</v>
-      </c>
-      <c r="Q57" s="173" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="R57" s="173" t="n">
-        <v>0</v>
-      </c>
+      <c r="O57" s="342" t="n"/>
+      <c r="P57" s="173" t="n"/>
+      <c r="Q57" s="173" t="n"/>
+      <c r="R57" s="173" t="n"/>
       <c r="S57" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="58" s="153" thickBot="1">
@@ -21195,18 +20993,10 @@
           <t>Pérdidas en las líneas</t>
         </is>
       </c>
-      <c r="O58" s="347" t="n">
-        <v>49.86</v>
-      </c>
-      <c r="P58" s="166" t="n">
-        <v>70.05</v>
-      </c>
-      <c r="Q58" s="166" t="n">
-        <v>85.98999999999999</v>
-      </c>
-      <c r="R58" s="166" t="n">
-        <v>57.99</v>
-      </c>
+      <c r="O58" s="347" t="n"/>
+      <c r="P58" s="166" t="n"/>
+      <c r="Q58" s="166" t="n"/>
+      <c r="R58" s="166" t="n"/>
       <c r="S58" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="59" s="153" thickBot="1">
@@ -21221,18 +21011,10 @@
           <t>Pérdidas en los cables</t>
         </is>
       </c>
-      <c r="O59" s="347" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P59" s="166" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Q59" s="166" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R59" s="166" t="n">
-        <v>77.17</v>
-      </c>
+      <c r="O59" s="347" t="n"/>
+      <c r="P59" s="166" t="n"/>
+      <c r="Q59" s="166" t="n"/>
+      <c r="R59" s="166" t="n"/>
       <c r="S59" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="26.25" r="60" s="153" thickBot="1">
@@ -21247,18 +21029,10 @@
           <t>Pérdidas de carga del transformador</t>
         </is>
       </c>
-      <c r="O60" s="347" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="166" t="n">
-        <v>0</v>
-      </c>
+      <c r="O60" s="347" t="n"/>
+      <c r="P60" s="166" t="n"/>
+      <c r="Q60" s="166" t="n"/>
+      <c r="R60" s="166" t="n"/>
       <c r="S60" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="61" s="153" thickBot="1">
@@ -21273,18 +21047,10 @@
           <t>Pérdidas en vacío del transformador</t>
         </is>
       </c>
-      <c r="O61" s="347" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="166" t="n">
-        <v>0</v>
-      </c>
+      <c r="O61" s="347" t="n"/>
+      <c r="P61" s="166" t="n"/>
+      <c r="Q61" s="166" t="n"/>
+      <c r="R61" s="166" t="n"/>
       <c r="S61" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="62" s="153" thickBot="1">
@@ -21299,18 +21065,10 @@
           <t>Pérdidas totales</t>
         </is>
       </c>
-      <c r="O62" s="342" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="P62" s="173" t="n">
-        <v>71.09</v>
-      </c>
-      <c r="Q62" s="173" t="n">
-        <v>87.56</v>
-      </c>
-      <c r="R62" s="173" t="n">
-        <v>58.38</v>
-      </c>
+      <c r="O62" s="342" t="n"/>
+      <c r="P62" s="173" t="n"/>
+      <c r="Q62" s="173" t="n"/>
+      <c r="R62" s="173" t="n"/>
       <c r="S62" s="175" t="n"/>
     </row>
     <row customFormat="1" r="63" s="153">

--- a/doc/justificacion.xlsx
+++ b/doc/justificacion.xlsx
@@ -5742,7 +5742,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="es-PE"/>
           </a:p>
@@ -5833,7 +5833,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="es-PE"/>
           </a:p>
@@ -5935,6 +5935,433 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>4</col>
+      <colOff>254000</colOff>
+      <row>147</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>9</col>
+      <colOff>701674</colOff>
+      <row>164</row>
+      <rowOff>14536</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Imagen 6"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="4806950" y="28489275"/>
+          <a:ext cx="5635624" cy="3246686"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr lastClr="000000" val="windowText"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>4</col>
+      <colOff>471715</colOff>
+      <row>37</row>
+      <rowOff>54427</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>154216</colOff>
+      <row>54</row>
+      <rowOff>133443</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 2"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="5243286" y="7810498"/>
+          <a:ext cx="5923644" cy="3471731"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr lastClr="000000" val="windowText"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>4</col>
+      <colOff>514350</colOff>
+      <row>66</row>
+      <rowOff>180975</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>739775</colOff>
+      <row>83</row>
+      <rowOff>15875</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Imagen 23"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="5067300" y="13239750"/>
+          <a:ext cx="6172200" cy="3067050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr lastClr="000000" val="windowText"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>4</col>
+      <colOff>889908</colOff>
+      <row>117</row>
+      <rowOff>110672</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>381907</colOff>
+      <row>133</row>
+      <rowOff>131077</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Imagen 15"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="5442858" y="22884947"/>
+          <a:ext cx="5445124" cy="3065230"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr lastClr="000000" val="windowText"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>702576</colOff>
+      <row>115</row>
+      <rowOff>73395</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>403893</colOff>
+      <row>126</row>
+      <rowOff>36285</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Imagen 26"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="702576" y="23396038"/>
+          <a:ext cx="4472888" cy="2158176"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>752475</colOff>
+      <row>146</row>
+      <rowOff>123825</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>206375</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Imagen 34"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="752475" y="28422600"/>
+          <a:ext cx="4000500" cy="2162175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>19050</colOff>
+      <row>67</row>
+      <rowOff>104775</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>114300</colOff>
+      <row>79</row>
+      <rowOff>53975</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Imagen 37"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="781050" y="13354050"/>
+          <a:ext cx="3886200" cy="2228850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>698500</colOff>
+      <row>40</row>
+      <rowOff>3175</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>145076</colOff>
+      <row>50</row>
+      <rowOff>91639</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="698500" y="8108950"/>
+          <a:ext cx="3993176" cy="1993464"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>444500</colOff>
+      <row>109</row>
+      <rowOff>45357</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>76340</colOff>
+      <row>120</row>
+      <rowOff>136390</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Imagen 16"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="12255500" y="22170571"/>
+          <a:ext cx="4258269" cy="2286319"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>11</col>
+      <colOff>435429</colOff>
+      <row>117</row>
+      <rowOff>117928</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>153006</colOff>
+      <row>129</row>
+      <rowOff>34793</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Imagen 17"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="12246429" y="23839714"/>
+          <a:ext cx="4344006" cy="2305372"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
@@ -5961,6 +6388,93 @@
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>1011465</colOff>
+      <row>8</row>
+      <rowOff>142875</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>54097</colOff>
+      <row>20</row>
+      <rowOff>76678</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="20283715" y="1666875"/>
+          <a:ext cx="4097232" cy="2195130"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>20</col>
+      <colOff>1183408</colOff>
+      <row>32</row>
+      <rowOff>77932</rowOff>
+    </from>
+    <to>
+      <col>23</col>
+      <colOff>306539</colOff>
+      <row>43</row>
+      <rowOff>170295</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 2"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="20455658" y="6316807"/>
+          <a:ext cx="4187256" cy="2187864"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
     <clientData/>
   </twoCellAnchor>
 </wsDr>
@@ -15360,12 +15874,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:K214"/>
+  <dimension ref="A1:K214"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" max="1" min="1" style="137" width="11.42578125"/>
@@ -15381,6 +15895,7 @@
     <col customWidth="1" max="13" min="13" width="11.5703125"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="C2" s="138" t="inlineStr">
         <is>
@@ -15398,11 +15913,7 @@
           <t>Cliente:</t>
         </is>
       </c>
-      <c r="C4" s="140" t="inlineStr">
-        <is>
-          <t>San Fernando S.A (RUC 20100154308)</t>
-        </is>
-      </c>
+      <c r="C4" s="140" t="inlineStr"/>
       <c r="D4" s="140" t="n"/>
       <c r="E4" s="140" t="n"/>
       <c r="H4" s="141" t="n"/>
@@ -15416,7 +15927,7 @@
       </c>
       <c r="C5" s="140" t="inlineStr">
         <is>
-          <t>Sector Santa Fe de Lanchas,  Unidad Catastral 72869, distrito de Paracas, provincia de Pisco y departamento de Ica</t>
+          <t>Electro Dunas</t>
         </is>
       </c>
       <c r="D5" s="140" t="n"/>
@@ -15433,14 +15944,14 @@
       </c>
       <c r="C6" s="140" t="inlineStr">
         <is>
-          <t>Solicitud de factibilidad y punto de diseño en media tensión</t>
+          <t>Factibilidad y Punto de Diseño</t>
         </is>
       </c>
       <c r="D6" s="140" t="n"/>
       <c r="E6" s="140" t="n"/>
       <c r="H6" s="350" t="inlineStr">
         <is>
-          <t>1420KW</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="350" t="n"/>
@@ -15452,7 +15963,7 @@
         </is>
       </c>
       <c r="C7" s="494" t="n">
-        <v>1420</v>
+        <v>680</v>
       </c>
       <c r="G7" s="141" t="inlineStr">
         <is>
@@ -15460,7 +15971,7 @@
         </is>
       </c>
       <c r="H7" s="373" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="8">
@@ -15471,7 +15982,7 @@
       </c>
       <c r="C8" s="140" t="inlineStr">
         <is>
-          <t>PA217</t>
+          <t>CA101</t>
         </is>
       </c>
       <c r="D8" s="140" t="n"/>
@@ -15483,7 +15994,7 @@
       </c>
       <c r="H8" s="137" t="inlineStr">
         <is>
-          <t>SET Paracas</t>
+          <t>SET CA101</t>
         </is>
       </c>
     </row>
@@ -15494,7 +16005,7 @@
         </is>
       </c>
       <c r="C9" s="140" t="n">
-        <v>22.9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="140" t="n"/>
       <c r="E9" s="140" t="n"/>
@@ -15505,7 +16016,7 @@
       </c>
       <c r="H9" s="137" t="inlineStr">
         <is>
-          <t>Transformador SET Paracas · 22.9 kV (inventario CYMDIST)</t>
+          <t>Transformador SET CA101 · 10.0 kV (inventario CYMDIST)</t>
         </is>
       </c>
     </row>
@@ -15517,7 +16028,7 @@
       </c>
       <c r="C10" s="137" t="inlineStr">
         <is>
-          <t>CARTA G T-SU-966-2026/PO</t>
+          <t>RECYM-CA101</t>
         </is>
       </c>
       <c r="D10" s="140" t="n"/>
@@ -15630,6 +16141,8 @@
     <row customHeight="1" ht="15" r="23">
       <c r="B23" s="479" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="B26" s="143" t="inlineStr">
         <is>
@@ -15645,6 +16158,7 @@
       <c r="I26" s="143" t="n"/>
       <c r="J26" s="143" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="138" t="inlineStr">
         <is>
@@ -15652,6 +16166,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row customHeight="1" ht="15.75" r="30">
       <c r="B30" s="603" t="n"/>
       <c r="C30" s="604" t="n"/>
@@ -15699,15 +16214,15 @@
       <c r="C32" s="610" t="n"/>
       <c r="D32" s="611" t="n"/>
       <c r="E32" s="392">
-        <f>'Resultados de escenarios'!O14</f>
+        <f>'Resultados de escenarios'!H5</f>
         <v/>
       </c>
       <c r="F32" s="392">
-        <f>'Resultados de escenarios'!P14</f>
+        <f>+'Resultados de escenarios'!I5</f>
         <v/>
       </c>
       <c r="G32" s="392">
-        <f>'Resultados de escenarios'!Q14</f>
+        <f>+'Resultados de escenarios'!G5</f>
         <v/>
       </c>
       <c r="H32" s="393">
@@ -15828,6 +16343,33 @@
       <c r="G39" s="144" t="n"/>
       <c r="H39" s="144" t="n"/>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
     <row r="67">
       <c r="B67" s="138" t="inlineStr">
         <is>
@@ -15835,6 +16377,7 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="C69" s="140" t="n"/>
       <c r="D69" s="140" t="n"/>
@@ -15843,10 +16386,41 @@
       <c r="G69" s="144" t="n"/>
       <c r="H69" s="144" t="n"/>
     </row>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
     <row r="101">
       <c r="B101" s="143" t="inlineStr">
         <is>
-          <t>2.1 RED PROYECTADA DE ELECTRODUNAS PA217</t>
+          <t>2.1 RED PROYECTADA DE ELECTRODUNAS LL202</t>
         </is>
       </c>
       <c r="C101" s="143" t="n"/>
@@ -15858,6 +16432,7 @@
       <c r="I101" s="143" t="n"/>
       <c r="J101" s="143" t="n"/>
     </row>
+    <row r="102"/>
     <row r="103">
       <c r="B103" s="138" t="inlineStr">
         <is>
@@ -15865,6 +16440,7 @@
         </is>
       </c>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="B105" s="603" t="n"/>
       <c r="C105" s="604" t="n"/>
@@ -16036,6 +16612,34 @@
       <c r="G114" s="144" t="n"/>
       <c r="H114" s="144" t="n"/>
     </row>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
     <row r="143">
       <c r="B143" s="138" t="inlineStr">
         <is>
@@ -16046,6 +16650,33 @@
     <row customHeight="1" ht="6.75" r="144"/>
     <row customHeight="1" ht="6.75" r="145"/>
     <row customHeight="1" ht="6.75" r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
     <row r="174">
       <c r="B174" s="138" t="inlineStr">
         <is>
@@ -16128,7 +16759,7 @@
     <row r="181">
       <c r="B181" s="137" t="inlineStr">
         <is>
-          <t>PERDIDAS OBTENIDAS DE ESTUDIOS REALIZADOS AL ALIMENTADOR PA217 (Incorporando cargas solicitadas)</t>
+          <t>PERDIDAS OBTENIDAS DE ESTUDIOS REALIZADOS AL ALIMENTADOR SL201 (Incorporando cargas solicitadas)</t>
         </is>
       </c>
     </row>
@@ -16188,7 +16819,7 @@
     <row customHeight="1" ht="28.5" r="185">
       <c r="B185" s="480" t="inlineStr">
         <is>
-          <t>ESTADO ACTUAL PA217</t>
+          <t>ESTADO ACTUAL LL202</t>
         </is>
       </c>
       <c r="C185" s="385">
@@ -16215,7 +16846,7 @@
     <row customHeight="1" ht="28.5" r="186">
       <c r="B186" s="480" t="inlineStr">
         <is>
-          <t>ESTADO PROYECTADO PA217</t>
+          <t>ESTADO PRYECTADO LL202</t>
         </is>
       </c>
       <c r="C186" s="385">
@@ -16447,6 +17078,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="173" man="1" max="10" min="0"/>
   </rowBreaks>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19400,7 +20032,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -19437,7 +20069,7 @@
     <row r="2">
       <c r="A2" s="504" t="inlineStr">
         <is>
-          <t>ESCENARIO ACTUAL DEL ALIMENTADOR PA217</t>
+          <t>ESCENARIO ACTUAL DEL ALIMENTADOR CA101</t>
         </is>
       </c>
       <c r="F2" s="503" t="n"/>
@@ -19505,25 +20137,25 @@
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="5" s="153" thickBot="1">
       <c r="C5" s="380" t="n">
-        <v>0.9984</v>
+        <v>0.802</v>
       </c>
       <c r="D5" s="381" t="n">
-        <v>22.9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="381" t="n">
-        <v>13.2</v>
+        <v>5.8</v>
       </c>
       <c r="F5" s="381" t="n">
-        <v>169.8</v>
+        <v>175.3</v>
       </c>
       <c r="G5" s="381" t="n">
-        <v>6736.6</v>
+        <v>3036.95</v>
       </c>
       <c r="H5" s="381" t="n">
-        <v>6498</v>
+        <v>3022</v>
       </c>
       <c r="I5" s="381" t="n">
-        <v>1777</v>
+        <v>301</v>
       </c>
     </row>
     <row customFormat="1" r="6" s="153">
@@ -19679,16 +20311,16 @@
         </is>
       </c>
       <c r="O12" s="346" t="n">
-        <v>6498</v>
+        <v>3022</v>
       </c>
       <c r="P12" s="164" t="n">
-        <v>1777</v>
+        <v>301</v>
       </c>
       <c r="Q12" s="164" t="n">
-        <v>6736.6</v>
+        <v>3036.95</v>
       </c>
       <c r="R12" s="164" t="n">
-        <v>96.45999999999999</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="13" s="153" thickBot="1">
@@ -19767,16 +20399,16 @@
         </is>
       </c>
       <c r="O14" s="342" t="n">
-        <v>6498</v>
+        <v>3022</v>
       </c>
       <c r="P14" s="173" t="n">
-        <v>1777</v>
+        <v>301</v>
       </c>
       <c r="Q14" s="173" t="n">
-        <v>6736.6</v>
+        <v>3036.95</v>
       </c>
       <c r="R14" s="173" t="n">
-        <v>96.45999999999999</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="15" s="153" thickBot="1">
@@ -19809,7 +20441,7 @@
       </c>
       <c r="K15" s="166" t="n"/>
       <c r="L15" s="167" t="n">
-        <v>0.9984</v>
+        <v>0.802</v>
       </c>
       <c r="N15" s="171" t="inlineStr">
         <is>
@@ -19817,16 +20449,16 @@
         </is>
       </c>
       <c r="O15" s="347" t="n">
-        <v>6498</v>
+        <v>3022</v>
       </c>
       <c r="P15" s="166" t="n">
-        <v>1777</v>
+        <v>301</v>
       </c>
       <c r="Q15" s="166" t="n">
-        <v>6736.6</v>
+        <v>3036.95</v>
       </c>
       <c r="R15" s="166" t="n">
-        <v>96.45999999999999</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="16" s="153" thickBot="1">
@@ -19849,7 +20481,7 @@
       </c>
       <c r="K16" s="166" t="n"/>
       <c r="L16" s="167" t="n">
-        <v>0.9984</v>
+        <v>0.802</v>
       </c>
       <c r="N16" s="171" t="inlineStr">
         <is>
@@ -19857,16 +20489,16 @@
         </is>
       </c>
       <c r="O16" s="347" t="n">
-        <v>6498</v>
+        <v>3022</v>
       </c>
       <c r="P16" s="166" t="n">
-        <v>1777</v>
+        <v>301</v>
       </c>
       <c r="Q16" s="166" t="n">
-        <v>6736.6</v>
+        <v>3036.95</v>
       </c>
       <c r="R16" s="166" t="n">
-        <v>96.45999999999999</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="17" s="153" thickBot="1">
@@ -19881,7 +20513,7 @@
       </c>
       <c r="K17" s="168" t="n"/>
       <c r="L17" s="169" t="n">
-        <v>0.9984</v>
+        <v>0.802</v>
       </c>
       <c r="N17" s="171" t="inlineStr">
         <is>
@@ -20002,16 +20634,16 @@
         </is>
       </c>
       <c r="O20" s="342" t="n">
-        <v>6498</v>
+        <v>3022</v>
       </c>
       <c r="P20" s="173" t="n">
-        <v>1777</v>
+        <v>301</v>
       </c>
       <c r="Q20" s="173" t="n">
-        <v>6736.6</v>
+        <v>3036.95</v>
       </c>
       <c r="R20" s="173" t="n">
-        <v>96.45999999999999</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="21" s="153" thickBot="1">
@@ -20221,7 +20853,7 @@
       <c r="A34" s="179" t="n"/>
       <c r="B34" s="504" t="inlineStr">
         <is>
-          <t>ESCENARIO PROYECTADO DEL ALIMENTADOR PA217</t>
+          <t>ESCENARIO PROYECTADO DEL ALIMENTADOR A LL202</t>
         </is>
       </c>
       <c r="I34" s="174" t="n"/>
@@ -20342,25 +20974,25 @@
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="39" s="153" thickBot="1">
       <c r="C39" s="380" t="n">
-        <v>0.9984</v>
+        <v>0.99</v>
       </c>
       <c r="D39" s="381" t="n">
-        <v>22.9</v>
+        <v>9.9</v>
       </c>
       <c r="E39" s="381" t="n">
-        <v>13.2</v>
+        <v>5.7</v>
       </c>
       <c r="F39" s="381" t="n">
-        <v>169.8</v>
+        <v>199</v>
       </c>
       <c r="G39" s="381" t="n">
-        <v>6736.6</v>
+        <v>3233.12</v>
       </c>
       <c r="H39" s="381" t="n">
-        <v>6498</v>
+        <v>3233.12</v>
       </c>
       <c r="I39" s="381" t="n">
-        <v>1777</v>
+        <v>1156.66</v>
       </c>
       <c r="J39" s="175" t="n"/>
       <c r="K39" s="175" t="n"/>
@@ -20551,9 +21183,15 @@
           <t>Pérdidas en las líneas</t>
         </is>
       </c>
-      <c r="C46" s="346" t="n"/>
-      <c r="D46" s="164" t="n"/>
-      <c r="E46" s="164" t="n"/>
+      <c r="C46" s="346" t="n">
+        <v>157.61</v>
+      </c>
+      <c r="D46" s="164" t="n">
+        <v>505.5</v>
+      </c>
+      <c r="E46" s="164" t="n">
+        <v>50.55</v>
+      </c>
       <c r="H46" s="156" t="inlineStr">
         <is>
           <t>Sobrecarga</t>
@@ -20565,26 +21203,32 @@
         </is>
       </c>
       <c r="J46" s="387" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="164" t="n"/>
-      <c r="L46" s="165" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="K46" s="164" t="inlineStr">
+        <is>
+          <t>SEC_2010_329525_SE70004</t>
+        </is>
+      </c>
+      <c r="L46" s="165" t="n">
+        <v>1.7367</v>
+      </c>
       <c r="N46" s="170" t="inlineStr">
         <is>
           <t>Fuentes (Potencia de equilibrio)</t>
         </is>
       </c>
       <c r="O46" s="346" t="n">
-        <v>6498</v>
+        <v>3233.12</v>
       </c>
       <c r="P46" s="164" t="n">
-        <v>1777</v>
+        <v>1156.66</v>
       </c>
       <c r="Q46" s="164" t="n">
-        <v>6736.6</v>
+        <v>3433.79</v>
       </c>
       <c r="R46" s="164" t="n">
-        <v>96.45999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="S46" s="175" t="n"/>
     </row>
@@ -20611,10 +21255,16 @@
         </is>
       </c>
       <c r="J47" s="388" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="166" t="n"/>
-      <c r="L47" s="167" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K47" s="166" t="inlineStr">
+        <is>
+          <t>SEC_2010_329525_SE70004</t>
+        </is>
+      </c>
+      <c r="L47" s="167" t="n">
+        <v>1.7366</v>
+      </c>
       <c r="N47" s="171" t="inlineStr">
         <is>
           <t>Generadores</t>
@@ -20657,26 +21307,32 @@
         </is>
       </c>
       <c r="J48" s="389" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="168" t="n"/>
-      <c r="L48" s="169" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="168" t="inlineStr">
+        <is>
+          <t>SEC_2010_329525_SE70004</t>
+        </is>
+      </c>
+      <c r="L48" s="169" t="n">
+        <v>1.7368</v>
+      </c>
       <c r="N48" s="172" t="inlineStr">
         <is>
           <t>Producción total</t>
         </is>
       </c>
       <c r="O48" s="342" t="n">
-        <v>6498</v>
+        <v>3233.12</v>
       </c>
       <c r="P48" s="173" t="n">
-        <v>1777</v>
+        <v>1156.66</v>
       </c>
       <c r="Q48" s="173" t="n">
-        <v>6736.6</v>
+        <v>3433.79</v>
       </c>
       <c r="R48" s="173" t="n">
-        <v>96.45999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="S48" s="175" t="n"/>
     </row>
@@ -20709,9 +21365,11 @@
       <c r="J49" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="166" t="n"/>
+      <c r="K49" s="166" t="n">
+        <v>37</v>
+      </c>
       <c r="L49" s="167" t="n">
-        <v>0.9984</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="N49" s="171" t="inlineStr">
         <is>
@@ -20719,16 +21377,16 @@
         </is>
       </c>
       <c r="O49" s="347" t="n">
-        <v>6498</v>
+        <v>3182.04</v>
       </c>
       <c r="P49" s="166" t="n">
-        <v>1777</v>
+        <v>1101.44</v>
       </c>
       <c r="Q49" s="166" t="n">
-        <v>6736.6</v>
+        <v>3367.28</v>
       </c>
       <c r="R49" s="166" t="n">
-        <v>96.45999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="S49" s="175" t="n"/>
     </row>
@@ -20739,9 +21397,15 @@
           <t>Pérdidas totales</t>
         </is>
       </c>
-      <c r="C50" s="342" t="n"/>
-      <c r="D50" s="173" t="n"/>
-      <c r="E50" s="173" t="n"/>
+      <c r="C50" s="342" t="n">
+        <v>157.61</v>
+      </c>
+      <c r="D50" s="173" t="n">
+        <v>505.5</v>
+      </c>
+      <c r="E50" s="173" t="n">
+        <v>50.55</v>
+      </c>
       <c r="H50" s="157" t="n"/>
       <c r="I50" s="344" t="inlineStr">
         <is>
@@ -20751,9 +21415,11 @@
       <c r="J50" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K50" s="166" t="n"/>
+      <c r="K50" s="166" t="n">
+        <v>37</v>
+      </c>
       <c r="L50" s="167" t="n">
-        <v>0.9984</v>
+        <v>0.9599</v>
       </c>
       <c r="N50" s="171" t="inlineStr">
         <is>
@@ -20761,16 +21427,16 @@
         </is>
       </c>
       <c r="O50" s="347" t="n">
-        <v>6498</v>
+        <v>3182</v>
       </c>
       <c r="P50" s="166" t="n">
-        <v>1777</v>
+        <v>1101.38</v>
       </c>
       <c r="Q50" s="166" t="n">
-        <v>6736.6</v>
+        <v>3367.22</v>
       </c>
       <c r="R50" s="166" t="n">
-        <v>96.45999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="S50" s="175" t="n"/>
     </row>
@@ -20785,9 +21451,11 @@
       <c r="J51" s="389" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="168" t="n"/>
+      <c r="K51" s="168" t="n">
+        <v>37</v>
+      </c>
       <c r="L51" s="169" t="n">
-        <v>0.9984</v>
+        <v>0.9643</v>
       </c>
       <c r="N51" s="171" t="inlineStr">
         <is>
@@ -20829,8 +21497,14 @@
       <c r="J52" s="388" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="166" t="n"/>
-      <c r="L52" s="167" t="n"/>
+      <c r="K52" s="166" t="inlineStr">
+        <is>
+          <t>NET_2030_147_LL202</t>
+        </is>
+      </c>
+      <c r="L52" s="167" t="n">
+        <v>1.0483</v>
+      </c>
       <c r="N52" s="171" t="inlineStr">
         <is>
           <t>Reactancias shunt(reguladas)</t>
@@ -20867,8 +21541,14 @@
       <c r="J53" s="387" t="n">
         <v>0</v>
       </c>
-      <c r="K53" s="164" t="n"/>
-      <c r="L53" s="165" t="n"/>
+      <c r="K53" s="164" t="inlineStr">
+        <is>
+          <t>NET_2030_147_LL202</t>
+        </is>
+      </c>
+      <c r="L53" s="165" t="n">
+        <v>1.0483</v>
+      </c>
       <c r="N53" s="171" t="inlineStr">
         <is>
           <t>Motores</t>
@@ -20905,8 +21585,14 @@
       <c r="J54" s="389" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="168" t="n"/>
-      <c r="L54" s="169" t="n"/>
+      <c r="K54" s="168" t="inlineStr">
+        <is>
+          <t>NET_2030_147_LL202</t>
+        </is>
+      </c>
+      <c r="L54" s="169" t="n">
+        <v>1.0483</v>
+      </c>
       <c r="M54" s="177" t="n"/>
       <c r="N54" s="172" t="inlineStr">
         <is>
@@ -20914,16 +21600,16 @@
         </is>
       </c>
       <c r="O54" s="342" t="n">
-        <v>6498</v>
+        <v>3182</v>
       </c>
       <c r="P54" s="173" t="n">
-        <v>1777</v>
+        <v>1101.38</v>
       </c>
       <c r="Q54" s="173" t="n">
-        <v>6736.6</v>
+        <v>3367.22</v>
       </c>
       <c r="R54" s="173" t="n">
-        <v>96.45999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="S54" s="175" t="n"/>
     </row>
@@ -20939,10 +21625,18 @@
           <t>Capacitancia del cable</t>
         </is>
       </c>
-      <c r="O55" s="346" t="n"/>
-      <c r="P55" s="164" t="n"/>
-      <c r="Q55" s="164" t="n"/>
-      <c r="R55" s="164" t="n"/>
+      <c r="O55" s="346" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="164" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="Q55" s="164" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="R55" s="164" t="n">
+        <v>0</v>
+      </c>
       <c r="S55" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="56" s="153" thickBot="1">
@@ -20957,10 +21651,18 @@
           <t>Capacitancia de la línea</t>
         </is>
       </c>
-      <c r="O56" s="347" t="n"/>
-      <c r="P56" s="166" t="n"/>
-      <c r="Q56" s="166" t="n"/>
-      <c r="R56" s="166" t="n"/>
+      <c r="O56" s="347" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="166" t="n">
+        <v>-7.61</v>
+      </c>
+      <c r="Q56" s="166" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="R56" s="166" t="n">
+        <v>0</v>
+      </c>
       <c r="S56" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="57" s="153" thickBot="1">
@@ -20975,10 +21677,18 @@
           <t>Capacitancia shunt total</t>
         </is>
       </c>
-      <c r="O57" s="342" t="n"/>
-      <c r="P57" s="173" t="n"/>
-      <c r="Q57" s="173" t="n"/>
-      <c r="R57" s="173" t="n"/>
+      <c r="O57" s="342" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="173" t="n">
+        <v>-15.81</v>
+      </c>
+      <c r="Q57" s="173" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="R57" s="173" t="n">
+        <v>0</v>
+      </c>
       <c r="S57" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="58" s="153" thickBot="1">
@@ -20993,10 +21703,18 @@
           <t>Pérdidas en las líneas</t>
         </is>
       </c>
-      <c r="O58" s="347" t="n"/>
-      <c r="P58" s="166" t="n"/>
-      <c r="Q58" s="166" t="n"/>
-      <c r="R58" s="166" t="n"/>
+      <c r="O58" s="347" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="P58" s="166" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="Q58" s="166" t="n">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="R58" s="166" t="n">
+        <v>57.99</v>
+      </c>
       <c r="S58" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="59" s="153" thickBot="1">
@@ -21011,10 +21729,18 @@
           <t>Pérdidas en los cables</t>
         </is>
       </c>
-      <c r="O59" s="347" t="n"/>
-      <c r="P59" s="166" t="n"/>
-      <c r="Q59" s="166" t="n"/>
-      <c r="R59" s="166" t="n"/>
+      <c r="O59" s="347" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P59" s="166" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Q59" s="166" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R59" s="166" t="n">
+        <v>77.17</v>
+      </c>
       <c r="S59" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="26.25" r="60" s="153" thickBot="1">
@@ -21029,10 +21755,18 @@
           <t>Pérdidas de carga del transformador</t>
         </is>
       </c>
-      <c r="O60" s="347" t="n"/>
-      <c r="P60" s="166" t="n"/>
-      <c r="Q60" s="166" t="n"/>
-      <c r="R60" s="166" t="n"/>
+      <c r="O60" s="347" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="166" t="n">
+        <v>0</v>
+      </c>
       <c r="S60" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="61" s="153" thickBot="1">
@@ -21047,10 +21781,18 @@
           <t>Pérdidas en vacío del transformador</t>
         </is>
       </c>
-      <c r="O61" s="347" t="n"/>
-      <c r="P61" s="166" t="n"/>
-      <c r="Q61" s="166" t="n"/>
-      <c r="R61" s="166" t="n"/>
+      <c r="O61" s="347" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="166" t="n">
+        <v>0</v>
+      </c>
       <c r="S61" s="175" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="15.75" r="62" s="153" thickBot="1">
@@ -21065,10 +21807,18 @@
           <t>Pérdidas totales</t>
         </is>
       </c>
-      <c r="O62" s="342" t="n"/>
-      <c r="P62" s="173" t="n"/>
-      <c r="Q62" s="173" t="n"/>
-      <c r="R62" s="173" t="n"/>
+      <c r="O62" s="342" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="P62" s="173" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="Q62" s="173" t="n">
+        <v>87.56</v>
+      </c>
+      <c r="R62" s="173" t="n">
+        <v>58.38</v>
+      </c>
       <c r="S62" s="175" t="n"/>
     </row>
     <row customFormat="1" r="63" s="153">
@@ -21173,6 +21923,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
